--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -7874,7 +7874,7 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流云南站倒计时！</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流河北站倒计时！</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15834/</t>
+          <t>https://www.tiaozhanbei.net/article/15837/</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7948,7 +7948,7 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流河北站倒计时！</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15837/</t>
+          <t>https://www.tiaozhanbei.net/article/15838/</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8022,7 +8022,7 @@
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15838/</t>
+          <t>https://www.tiaozhanbei.net/article/15839/</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（三）</t>
+          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>https://mp.weixin.qq.com/s/Iu5xv-Nhr9wm7kit8_404Q?scene=1&amp;click_id=5</t>
+          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025.11.15</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -603,35 +603,39 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/tzb</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：动态。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -641,12 +645,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2025.11.15</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>挑战杯动态</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -656,12 +660,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -681,39 +685,35 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：动态。</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流河北站倒计时！</t>
+          <t>挑战杯丨关于举办第十五届“挑战杯”中国大学生创业计划竞赛的通知</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15837/</t>
+          <t>https://www.tiaozhanbei.net/article/15842/</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：培训。</t>
+          <t>标题疑似导航/资讯/培训内容：通知。</t>
         </is>
       </c>
     </row>

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -18,11 +18,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,8 +448,8 @@
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -789,29 +789,25 @@
           <t>报名/报名截止</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>具体日期</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026年9月10日</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>CFA Institute Research Challenge</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -821,37 +817,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -859,94 +855,94 @@
           <t>否</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>时间为周期性描述或需回源确认。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>具体日期</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026年9月10日</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>CFA Institute Research Challenge</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P1 优先关注</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>92</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：中国知网。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
@@ -1024,7 +1020,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
@@ -1035,17 +1031,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年秋季至冬季报名</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>CFA Institute Research Challenge</t>
+          <t>MCM/ICM 美国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1055,37 +1051,37 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1102,7 +1098,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
@@ -1113,17 +1109,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年2月</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>CFA Institute Research Challenge</t>
+          <t>MCM/ICM 美国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1133,37 +1129,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1180,7 +1176,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
@@ -1191,7 +1187,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>通常每年秋季至冬季报名</t>
+          <t>通常每年春季公布</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1258,7 +1254,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
@@ -1269,12 +1265,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>通常每年2月</t>
+          <t>每年春季至暑期关注学校通知</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>MCM/ICM 美国大学生数学建模竞赛</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1314,12 +1310,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1336,7 +1332,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
@@ -1347,12 +1343,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季公布</t>
+          <t>通常每年9月</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>MCM/ICM 美国大学生数学建模竞赛</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1392,12 +1388,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1414,7 +1410,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
@@ -1425,7 +1421,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>通常每年9月</t>
+          <t>通常赛后数月公示</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1492,7 +1488,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
@@ -1503,32 +1499,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>通常赛后数月公示</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1538,22 +1534,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1570,7 +1566,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
@@ -1648,7 +1644,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
@@ -1726,7 +1722,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
@@ -1742,7 +1738,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1777,19 +1773,11 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.datafountain.cn/competitions</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.datafountain.cn/competitions</t>
-        </is>
-      </c>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1804,7 +1792,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
@@ -1874,7 +1862,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
@@ -1944,7 +1932,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
@@ -1960,12 +1948,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1975,31 +1963,39 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>http://www.3chuang.net/</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>http://www.3chuang.net/</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -2014,7 +2010,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
@@ -2092,7 +2088,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
@@ -2170,7 +2166,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
@@ -2186,7 +2182,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2201,7 +2197,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2211,7 +2207,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2221,17 +2217,17 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>58</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2248,7 +2244,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
@@ -2326,7 +2322,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
@@ -2420,12 +2416,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2435,17 +2431,17 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2455,17 +2451,17 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2482,7 +2478,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
@@ -2498,7 +2494,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2538,12 +2534,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2560,7 +2556,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
@@ -2638,7 +2634,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
@@ -2716,7 +2712,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
@@ -2732,22 +2728,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2757,7 +2753,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2767,17 +2763,17 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -2794,7 +2790,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
@@ -2872,7 +2868,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -2950,7 +2946,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
@@ -2961,17 +2957,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3001,17 +2997,17 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -3028,7 +3024,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
@@ -3039,7 +3035,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季</t>
+          <t>通常每年春季初赛/决赛</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3106,7 +3102,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
@@ -3117,7 +3113,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3184,28 +3180,28 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>疑似误提取</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2009-20</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3215,7 +3211,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -3225,7 +3221,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3235,27 +3231,27 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/article/15839/</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>标题疑似导航/资讯/培训内容：培训。</t>
         </is>
       </c>
     </row>
@@ -3698,14 +3694,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -3713,8 +3709,8 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
-    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
@@ -3801,86 +3797,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>报名/报名截止</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>具体日期</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>全国大学生数学建模竞赛</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>数学建模类</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>P1 优先关注</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P2"/>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4006,14 +3924,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -4021,8 +3939,8 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
-    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
@@ -4109,86 +4027,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>报名/报名截止</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>具体日期</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>全国大学生数学建模竞赛</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>数学建模类</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>P1 优先关注</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P2"/>
+  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4199,13 +4039,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -4773,7 +4613,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
@@ -4784,7 +4624,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>通常每年9月</t>
+          <t>每年春季至暑期关注学校通知</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4851,7 +4691,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
@@ -4862,7 +4702,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>通常赛后数月公示</t>
+          <t>通常每年9月</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4929,7 +4769,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
@@ -4940,32 +4780,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常赛后数月公示</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P1 优先关注</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4975,22 +4815,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -5007,7 +4847,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
@@ -5085,7 +4925,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
@@ -5163,7 +5003,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
@@ -5179,7 +5019,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -5214,11 +5054,19 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -5233,7 +5081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
@@ -5303,7 +5151,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
@@ -5373,7 +5221,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
@@ -5389,12 +5237,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5404,39 +5252,31 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>http://www.3chuang.net/</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>http://www.3chuang.net/</t>
-        </is>
-      </c>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -5451,7 +5291,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
@@ -5529,7 +5369,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
@@ -5607,7 +5447,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
@@ -5623,7 +5463,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5638,7 +5478,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5648,7 +5488,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -5658,17 +5498,17 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -5685,7 +5525,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
@@ -5763,7 +5603,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
@@ -5857,12 +5697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5872,17 +5712,17 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -5892,17 +5732,17 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>58</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -5919,7 +5759,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
@@ -5935,7 +5775,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5975,12 +5815,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -5997,7 +5837,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
@@ -6075,7 +5915,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
@@ -6153,7 +5993,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
@@ -6169,22 +6009,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6194,7 +6034,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -6204,17 +6044,17 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -6231,7 +6071,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
@@ -6309,7 +6149,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
@@ -6387,7 +6227,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
@@ -6398,17 +6238,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6438,17 +6278,17 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -6465,7 +6305,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
@@ -6476,7 +6316,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
+          <t>通常每年春季</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6543,7 +6383,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
@@ -6554,7 +6394,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季初赛/决赛</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -6621,7 +6461,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -6637,12 +6477,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6652,7 +6492,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6662,7 +6502,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -6677,12 +6517,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -6699,7 +6539,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
@@ -6777,7 +6617,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
@@ -6852,8 +6692,86 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>结果公布/获奖公示</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯中国大学生创业计划竞赛</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>时间为周期性描述或需回源确认。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P34"/>
+  <autoFilter ref="A1:P35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6864,7 +6782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6882,7 +6800,7 @@
     <col width="42" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6982,12 +6900,12 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>CUMCM通讯2026年第1期（总第67期）</t>
+          <t>大数据和人工智能</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -6997,12 +6915,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -7012,22 +6930,22 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/cd6947d983e4a465e97c42c6ed0602af.html</t>
+          <t>https://www.datafountain.cn/competitions/1153</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -7037,7 +6955,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：通讯。</t>
+          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
         </is>
       </c>
     </row>
@@ -7056,12 +6974,12 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>SPSSPRO</t>
+          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -7071,12 +6989,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -7086,22 +7004,22 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://www.spsspro.com/?utm_source=cumcm</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -7111,7 +7029,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：SPSSPRO。</t>
+          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
         </is>
       </c>
     </row>
@@ -7130,12 +7048,12 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>《数学建模及其应用》</t>
+          <t>挑战杯丨关于举办第十五届“挑战杯”建设银行中国大学生创业计划竞赛的通知</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7150,32 +7068,32 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>http://qxyy.cbpt.cnki.net</t>
+          <t>https://www.tiaozhanbei.net/article/15842/</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -7185,7 +7103,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：《数学建模及其应用》。</t>
+          <t>标题疑似导航/资讯/培训内容：通知。</t>
         </is>
       </c>
     </row>
@@ -7201,34 +7119,30 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>报名时间: 2026年9月10日</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7238,22 +7152,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -7263,7 +7177,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：中国知网。</t>
+          <t>标题疑似编码异常或乱码。</t>
         </is>
       </c>
     </row>
@@ -7282,52 +7196,52 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>中国高校数学建模课程中心</t>
+          <t>大赛通知</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.icourses.cn/</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -7337,7 +7251,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：课程中心。</t>
+          <t>标题疑似导航/资讯/培训内容：通知。</t>
         </is>
       </c>
     </row>
@@ -7356,17 +7270,17 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>竞赛组织</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7376,32 +7290,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -7411,7 +7325,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：竞赛组织。</t>
+          <t>标题命中误抓取关键词：官方网站 移动版。</t>
         </is>
       </c>
     </row>
@@ -7430,52 +7344,52 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>苏州同元软控信息技术有限公司</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
+          <t>https://www.tiaozhanbei.net/article/15838/</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -7485,7 +7399,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：苏州同元软控信息技术有限公司。</t>
+          <t>标题疑似导航/资讯/培训内容：培训。</t>
         </is>
       </c>
     </row>
@@ -7501,55 +7415,59 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 2009-20</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>大数据和人工智能</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1153</t>
+          <t>https://www.tiaozhanbei.net/article/15839/</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -7559,7 +7477,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
+          <t>标题疑似导航/资讯/培训内容：培训。</t>
         </is>
       </c>
     </row>
@@ -7578,52 +7496,52 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
+          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -7633,7 +7551,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
+          <t>标题疑似导航/资讯/培训内容：笔记。</t>
         </is>
       </c>
     </row>
@@ -7649,15 +7567,19 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 2025.11.15</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7667,7 +7589,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7677,7 +7599,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -7692,12 +7614,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/tzb</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -7707,7 +7629,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>标题疑似编码异常或乱码。</t>
+          <t>标题疑似导航/资讯/培训内容：动态。</t>
         </is>
       </c>
     </row>
@@ -7723,10 +7645,14 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 6月1日</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>大赛通知</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -7761,17 +7687,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+          <t>https://www.tiaozhanbei.net/rules</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -7781,7 +7707,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：通知。</t>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7726,7 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>竞赛简介</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -7815,7 +7741,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7840,14 +7766,14 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/focus</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -7855,538 +7781,12 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：官方网站 移动版。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯丨关于举办第十五届“挑战杯”中国大学生创业计划竞赛的通知</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/article/15842/</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：通知。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/article/15838/</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：培训。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/article/15839/</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：培训。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：笔记。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>比赛时间: 2025.11.15</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯动态</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：动态。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>比赛时间: 6月1日</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>竞赛章程（大挑）</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>竞赛简介</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/focus</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
           <t>标题疑似导航/资讯/培训内容：简介。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P20"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,7 +16,7 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
@@ -442,14 +442,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -3180,23 +3180,23 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>疑似误提取</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15839/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3246,19 +3246,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：培训。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
@@ -3336,7 +3336,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
@@ -3414,7 +3414,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
@@ -3425,12 +3425,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>6月1日</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3465,110 +3465,32 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>正式比赛</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>6月1日</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>竞赛章程（大挑）</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
           <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P40"/>
+  <autoFilter ref="A1:P39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7415,11 +7337,7 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>比赛时间: 2009-20</t>
-        </is>
-      </c>
+      <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,7 +16,7 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
@@ -442,14 +442,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -3180,23 +3180,23 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>疑似误提取</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2009-20</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3231,34 +3231,34 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15838/</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>标题疑似导航/资讯/培训内容：培训。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
@@ -3336,7 +3336,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
@@ -3414,7 +3414,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
@@ -3425,72 +3425,150 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯中国大学生创业计划竞赛</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>时间为周期性描述或需回源确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>6月1日</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>竞赛章程（大挑）</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>创新创业类</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/rules</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P39"/>
+  <autoFilter ref="A1:P40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7263,7 +7341,11 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 2009-20</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,13 +16,13 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,14 +442,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -460,7 +460,7 @@
     <col width="42" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -548,12 +548,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025.11.15</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>挑战杯动态</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -603,39 +603,35 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：动态。</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -645,7 +641,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -713,7 +709,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -723,12 +719,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -768,12 +764,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -786,48 +782,52 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>具体日期</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>CFA Institute Research Challenge</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -837,17 +837,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -855,11 +855,7 @@
           <t>否</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>时间为周期性描述或需回源确认。</t>
-        </is>
-      </c>
+      <c r="P5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -867,30 +863,34 @@
           <t>正式比赛</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>具体日期</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>CFA Institute Research Challenge</t>
+          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -915,17 +915,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.tiaozhanbei.net/article/15846/</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -933,57 +933,57 @@
           <t>否</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>时间为周期性描述或需回源确认。</t>
-        </is>
-      </c>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr"/>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>具体日期</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>CFA Institute Research Challenge</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -993,112 +993,116 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>标题命中误抓取关键词：官方网站 移动版。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr"/>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>具体日期</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>通常每年秋季至冬季报名</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>MCM/ICM 美国大学生数学建模竞赛</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.tiaozhanbei.net/tzb</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>标题疑似导航/资讯/培训内容：动态。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
@@ -1109,17 +1113,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>通常每年2月</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>MCM/ICM 美国大学生数学建模竞赛</t>
+          <t>CFA Institute Research Challenge</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1129,37 +1133,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1176,7 +1180,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
@@ -1187,17 +1191,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季公布</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>MCM/ICM 美国大学生数学建模竞赛</t>
+          <t>CFA Institute Research Challenge</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1207,37 +1211,37 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>92</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1254,7 +1258,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
@@ -1265,17 +1269,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>每年春季至暑期关注学校通知</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>CFA Institute Research Challenge</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1285,37 +1289,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1332,7 +1336,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
@@ -1343,12 +1347,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>通常每年9月</t>
+          <t>通常每年秋季至冬季报名</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>MCM/ICM 美国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1388,12 +1392,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1410,7 +1414,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
@@ -1421,12 +1425,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>通常赛后数月公示</t>
+          <t>通常每年2月</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>MCM/ICM 美国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1466,12 +1470,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1488,7 +1492,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
@@ -1499,32 +1503,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季公布</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>MCM/ICM 美国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P1 优先关注</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1534,22 +1538,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1566,7 +1570,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
@@ -1577,32 +1581,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>每年春季至暑期关注学校通知</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P1 优先关注</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1612,22 +1616,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1644,7 +1648,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
@@ -1655,32 +1659,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年9月</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P1 优先关注</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1690,22 +1694,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1722,7 +1726,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
@@ -1733,32 +1737,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常赛后数月公示</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P1 优先关注</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1768,16 +1772,24 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mcm.edu.cn/index.moma</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mcm.edu.cn/index.moma</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1792,7 +1804,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
@@ -1808,7 +1820,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1843,11 +1855,19 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1862,7 +1882,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
@@ -1878,7 +1898,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1913,11 +1933,19 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1932,7 +1960,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
@@ -1948,12 +1976,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1963,37 +1991,37 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2010,7 +2038,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
@@ -2026,12 +2054,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2041,39 +2069,31 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>http://www.3chuang.net/</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>http://www.3chuang.net/</t>
-        </is>
-      </c>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -2088,7 +2108,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
@@ -2104,12 +2124,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2119,39 +2139,31 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>http://www.3chuang.net/</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>http://www.3chuang.net/</t>
-        </is>
-      </c>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -2166,7 +2178,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
@@ -2182,12 +2194,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2202,34 +2214,26 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>http://www.china-cssc.org/</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>http://www.china-cssc.org/</t>
-        </is>
-      </c>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -2244,7 +2248,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
@@ -2260,7 +2264,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2275,7 +2279,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2285,7 +2289,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2295,17 +2299,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2322,7 +2326,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
@@ -2338,7 +2342,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2353,7 +2357,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2363,7 +2367,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2373,17 +2377,17 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2416,12 +2420,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2436,12 +2440,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2456,12 +2460,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2494,12 +2498,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2509,17 +2513,17 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2529,17 +2533,17 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>58</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2572,12 +2576,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2587,17 +2591,17 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2607,17 +2611,17 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>58</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2650,12 +2654,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2665,17 +2669,17 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2685,17 +2689,17 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>58</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -2712,7 +2716,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
@@ -2728,22 +2732,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2753,7 +2757,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2763,17 +2767,17 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -2790,7 +2794,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
@@ -2806,22 +2810,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2831,7 +2835,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2841,17 +2845,17 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -2884,22 +2888,22 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2909,7 +2913,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2919,17 +2923,17 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -2957,27 +2961,27 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2987,7 +2991,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -3002,12 +3006,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -3024,7 +3028,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
@@ -3035,27 +3039,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -3065,7 +3069,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3080,12 +3084,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3102,7 +3106,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
@@ -3118,12 +3122,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3153,17 +3157,17 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -3186,22 +3190,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>疑似误提取</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3211,7 +3215,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -3221,7 +3225,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3231,34 +3235,34 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15838/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：培训。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
@@ -3274,12 +3278,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3289,7 +3293,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -3299,7 +3303,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3309,17 +3313,17 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3336,7 +3340,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
@@ -3347,17 +3351,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3367,7 +3371,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -3377,7 +3381,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3392,12 +3396,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3414,7 +3418,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
@@ -3425,17 +3429,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季初赛/决赛</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3445,7 +3449,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -3455,7 +3459,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3470,12 +3474,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -3492,7 +3496,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
@@ -3503,72 +3507,150 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>全国大学生英语竞赛</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>英语与财经表达类</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chinaneccs.cn/</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chinaneccs.cn/</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>时间为周期性描述或需回源确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>6月1日</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>竞赛章程（大挑）</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>创新创业类</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/rules</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P40"/>
+  <autoFilter ref="A1:P41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4039,7 +4121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5853,7 +5935,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5915,7 +5997,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
@@ -5931,7 +6013,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5993,7 +6075,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
@@ -6071,7 +6153,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
@@ -6087,22 +6169,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -6112,7 +6194,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -6122,17 +6204,17 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -6149,7 +6231,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
@@ -6227,7 +6309,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
@@ -6305,7 +6387,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
@@ -6316,17 +6398,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -6356,17 +6438,17 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -6383,7 +6465,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
@@ -6394,7 +6476,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
+          <t>通常每年春季</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -6461,7 +6543,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -6472,7 +6554,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季初赛/决赛</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6539,7 +6621,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
@@ -6555,12 +6637,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -6570,7 +6652,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -6580,7 +6662,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -6595,12 +6677,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -6614,164 +6696,8 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>正式比赛</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>时间为周期性描述或需回源确认。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>结果公布/获奖公示</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr"/>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>时间为周期性描述或需回源确认。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P35"/>
+  <autoFilter ref="A1:P33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6782,7 +6708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7267,7 +7193,11 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 2026.06.19</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
@@ -7343,12 +7273,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>比赛时间: 2009-20</t>
+          <t>比赛时间: 2026.06.19</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（云南站）顺利举办</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7388,7 +7318,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15838/</t>
+          <t>https://www.tiaozhanbei.net/tzb</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7403,7 +7333,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：培训。</t>
+          <t>标题疑似导航/资讯/培训内容：动态。</t>
         </is>
       </c>
     </row>
@@ -7419,10 +7349,14 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 6月1日</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”中国大学生创业计划竞赛培训交流（河北站）顺利举办</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -7462,7 +7396,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15839/</t>
+          <t>https://www.tiaozhanbei.net/rules</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7477,7 +7411,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：培训。</t>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7430,7 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨速来！“挑战杯”竞赛“学霸笔记”上新啦！（四）</t>
+          <t>竞赛简介</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -7536,7 +7470,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://mp.weixin.qq.com/s/my059Ww6twn2E5PeFiGWFg</t>
+          <t>https://www.tiaozhanbei.net/focus</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7551,242 +7485,12 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：笔记。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>比赛时间: 2025.11.15</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯动态</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：动态。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>比赛时间: 6月1日</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>竞赛章程（大挑）</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>竞赛简介</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/focus</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
           <t>标题疑似导航/资讯/培训内容：简介。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P13"/>
+  <autoFilter ref="A1:P10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,13 +16,13 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -724,7 +724,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -812,37 +812,37 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.tiaozhanbei.net/article/15846/</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15846/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -930,10 +930,14 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>标题命中误抓取关键词：官方网站 移动版。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -958,7 +962,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -973,7 +977,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -993,7 +997,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1008,14 +1012,10 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>标题命中误抓取关键词：官方网站 移动版。</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2966,22 +2966,22 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -3001,17 +3001,17 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
@@ -3044,22 +3044,22 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
@@ -3184,7 +3184,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
@@ -3273,17 +3273,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季初赛/决赛</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3313,17 +3313,17 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3340,7 +3340,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
@@ -3429,17 +3429,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3649,8 +3649,86 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>竞赛章程（小挑）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules2</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P41"/>
+  <autoFilter ref="A1:P42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5935,7 +6013,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -6013,7 +6091,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -6091,22 +6169,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6116,7 +6194,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -6126,17 +6204,17 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -6153,7 +6231,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
@@ -6169,22 +6247,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -6194,7 +6272,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -6204,17 +6282,17 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -6231,7 +6309,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
@@ -6309,7 +6387,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
@@ -6320,17 +6398,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6360,17 +6438,17 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -6387,7 +6465,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
@@ -6398,17 +6476,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季初赛/决赛</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -6438,17 +6516,17 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -6465,7 +6543,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
@@ -6476,7 +6554,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -6543,7 +6621,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -6554,17 +6632,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6574,7 +6652,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -6584,7 +6662,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -6599,12 +6677,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -6637,12 +6715,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -6652,7 +6730,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -6662,7 +6740,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -6677,12 +6755,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -6708,7 +6786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7427,70 +7505,148 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 6月1日</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>竞赛章程（小挑）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>竞赛简介</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>创新创业类</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/focus</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>标题疑似导航/资讯/培训内容：简介。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,13 +16,13 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,13 +442,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1105,25 +1105,29 @@
           <t>报名/报名截止</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>具体日期</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2026年9月10日</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>CFA Institute Research Challenge</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1133,37 +1137,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1171,94 +1175,94 @@
           <t>否</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>时间为周期性描述或需回源确认。</t>
-        </is>
-      </c>
+      <c r="P9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr"/>
+          <t>报名/报名截止</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>具体日期</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2026年9月10日</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>CFA Institute Research Challenge</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>https://www.cfainstitute.org/en/societies/challenge</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>标题命中误抓取关键词：中国知网。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
@@ -1336,7 +1340,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
@@ -1347,17 +1351,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>通常每年秋季至冬季报名</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>MCM/ICM 美国大学生数学建模竞赛</t>
+          <t>CFA Institute Research Challenge</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1367,37 +1371,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>92</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1414,7 +1418,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
@@ -1425,17 +1429,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>通常每年2月</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>MCM/ICM 美国大学生数学建模竞赛</t>
+          <t>CFA Institute Research Challenge</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>金融数学 / 金融科技 / 量化 / 风控相关比赛</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1445,37 +1449,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>https://www.comap.com/contests/mcm-icm</t>
+          <t>https://www.cfainstitute.org/en/societies/challenge</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1492,7 +1496,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
@@ -1503,7 +1507,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季公布</t>
+          <t>通常每年秋季至冬季报名</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1570,7 +1574,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
@@ -1581,12 +1585,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>每年春季至暑期关注学校通知</t>
+          <t>通常每年2月</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>MCM/ICM 美国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1626,12 +1630,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1648,7 +1652,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
@@ -1659,12 +1663,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>通常每年9月</t>
+          <t>通常每年春季公布</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>MCM/ICM 美国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1704,12 +1708,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.comap.com/contests/mcm-icm</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1726,7 +1730,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
@@ -1737,7 +1741,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>通常赛后数月公示</t>
+          <t>通常每年9月</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1804,7 +1808,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
@@ -1815,32 +1819,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常赛后数月公示</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>全国大学生数学建模竞赛</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P1 优先关注</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1850,22 +1854,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1882,7 +1886,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
@@ -1960,7 +1964,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
@@ -2038,7 +2042,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
@@ -2054,7 +2058,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2089,11 +2093,19 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.datafountain.cn/competitions</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -2108,7 +2120,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
@@ -2178,7 +2190,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
@@ -2248,7 +2260,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
@@ -2264,12 +2276,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2279,39 +2291,31 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>http://www.3chuang.net/</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>http://www.3chuang.net/</t>
-        </is>
-      </c>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -2326,7 +2330,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
@@ -2404,7 +2408,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
@@ -2482,7 +2486,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
@@ -2498,7 +2502,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2513,7 +2517,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2523,7 +2527,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2533,17 +2537,17 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>http://www.3chuang.net/</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2560,7 +2564,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
@@ -2638,7 +2642,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
@@ -2732,12 +2736,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2747,17 +2751,17 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2767,17 +2771,17 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>58</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -2794,7 +2798,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
@@ -2810,7 +2814,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2850,12 +2854,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -2872,7 +2876,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -2950,7 +2954,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
@@ -2966,22 +2970,22 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2991,7 +2995,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -3001,17 +3005,17 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -3028,7 +3032,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
@@ -3106,7 +3110,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
@@ -3184,7 +3188,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
@@ -3195,17 +3199,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3235,17 +3239,17 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3262,7 +3266,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
@@ -3273,7 +3277,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
+          <t>通常每年春季</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3340,7 +3344,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
@@ -3351,7 +3355,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季初赛/决赛</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3418,7 +3422,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
@@ -3434,12 +3438,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3449,7 +3453,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -3459,7 +3463,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3474,12 +3478,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -3496,7 +3500,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
@@ -3574,7 +3578,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
@@ -3585,12 +3589,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>6月1日</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3625,12 +3629,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3640,12 +3644,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
@@ -3668,67 +3672,145 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>竞赛章程（大挑）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>竞赛章程（小挑）</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>创新创业类</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr">
+      <c r="P43" s="2" t="inlineStr">
         <is>
           <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P42"/>
+  <autoFilter ref="A1:P43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3854,14 +3936,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -3869,8 +3951,8 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
@@ -3957,8 +4039,86 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>报名/报名截止</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>具体日期</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月10日</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>全国大学生数学建模竞赛</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>数学建模类</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>P1 优先关注</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mcm.edu.cn/index.moma</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mcm.edu.cn/index.moma</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4084,14 +4244,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -4099,8 +4259,8 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
@@ -4187,8 +4347,86 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>报名/报名截止</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>具体日期</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月10日</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>全国大学生数学建模竞赛</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>数学建模类</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>P1 优先关注</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mcm.edu.cn/index.moma</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mcm.edu.cn/index.moma</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4199,13 +4437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -4773,7 +5011,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
@@ -4784,7 +5022,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>每年春季至暑期关注学校通知</t>
+          <t>通常每年9月</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4851,7 +5089,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
@@ -4862,7 +5100,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>通常每年9月</t>
+          <t>通常赛后数月公示</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4929,7 +5167,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
@@ -4940,32 +5178,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>通常赛后数月公示</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>全国大学生数学建模竞赛</t>
+          <t>CCF 大数据与计算智能大赛 BDCI</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>P1 优先关注</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4975,22 +5213,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -5007,7 +5245,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
@@ -5085,7 +5323,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
@@ -5163,7 +5401,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
@@ -5179,7 +5417,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CCF 大数据与计算智能大赛 BDCI</t>
+          <t>全国大学生统计建模大赛</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -5214,19 +5452,11 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.datafountain.cn/competitions</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.datafountain.cn/competitions</t>
-        </is>
-      </c>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -5241,7 +5471,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
@@ -5311,7 +5541,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
@@ -5381,7 +5611,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
@@ -5397,12 +5627,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>全国大学生统计建模大赛</t>
+          <t>全国大学生电子商务创新创意创业挑战赛</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>商业案例分析类</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5412,31 +5642,39 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>http://www.3chuang.net/</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>http://www.3chuang.net/</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -5451,7 +5689,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
@@ -5529,7 +5767,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
@@ -5607,7 +5845,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
@@ -5623,7 +5861,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>全国大学生电子商务创新创意创业挑战赛</t>
+          <t>正大杯全国大学生市场调查与分析大赛</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5638,7 +5876,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5648,7 +5886,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -5658,17 +5896,17 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>58</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>http://www.3chuang.net/</t>
+          <t>http://www.china-cssc.org/</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -5685,7 +5923,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
@@ -5763,7 +6001,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
@@ -5857,12 +6095,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>正大杯全国大学生市场调查与分析大赛</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>商业案例分析类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5872,17 +6110,17 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -5892,17 +6130,17 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>http://www.china-cssc.org/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -5919,7 +6157,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
@@ -5935,7 +6173,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5975,12 +6213,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -5997,7 +6235,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
@@ -6075,7 +6313,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
@@ -6091,22 +6329,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>中国大学生计算机设计大赛</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>编程 / 算法 / AI 应用类</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6116,7 +6354,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -6126,17 +6364,17 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://jsjds.blcu.edu.cn/</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -6153,7 +6391,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
@@ -6231,7 +6469,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
@@ -6309,7 +6547,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
@@ -6320,17 +6558,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>通常每年春季</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>中国大学生计算机设计大赛</t>
+          <t>全国大学生英语竞赛</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>编程 / 算法 / AI 应用类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6360,17 +6598,17 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>https://jsjds.blcu.edu.cn/</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -6387,7 +6625,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
@@ -6398,7 +6636,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季</t>
+          <t>通常每年春季初赛/决赛</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -6465,7 +6703,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
@@ -6476,7 +6714,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>通常每年春季初赛/决赛</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6543,7 +6781,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
@@ -6559,12 +6797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>全国大学生英语竞赛</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6574,7 +6812,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -6584,7 +6822,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -6599,12 +6837,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -6621,7 +6859,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -6696,86 +6934,8 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>结果公布/获奖公示</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>时间为周期性描述或需回源确认。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P33"/>
+  <autoFilter ref="A1:P32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6786,7 +6946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6804,7 +6964,7 @@
     <col width="42" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6904,12 +7064,12 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>大数据和人工智能</t>
+          <t>2026年全国大学生数学建模竞赛培训与应用研究研讨会第二次通知</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -6919,12 +7079,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -6934,22 +7094,22 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1153</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/3703fb7f6e16f999f45aac0593b1e1ff.html</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -6959,7 +7119,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
+          <t>标题疑似导航/资讯/培训内容：通知。</t>
         </is>
       </c>
     </row>
@@ -6978,12 +7138,12 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
+          <t>SPSSPRO</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -6993,12 +7153,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -7008,22 +7168,22 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.spsspro.com/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -7033,7 +7193,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
+          <t>标题命中误抓取关键词：SPSSPRO。</t>
         </is>
       </c>
     </row>
@@ -7052,12 +7212,12 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨关于举办第十五届“挑战杯”建设银行中国大学生创业计划竞赛的通知</t>
+          <t>《数学建模及其应用》</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7072,32 +7232,32 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15842/</t>
+          <t>http://qxyy.cbpt.cnki.net</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -7107,7 +7267,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：通知。</t>
+          <t>标题命中误抓取关键词：《数学建模及其应用》。</t>
         </is>
       </c>
     </row>
@@ -7123,30 +7283,34 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>报名时间: 2026年9月10日</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7156,22 +7320,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -7181,7 +7345,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>标题疑似编码异常或乱码。</t>
+          <t>标题命中误抓取关键词：中国知网。</t>
         </is>
       </c>
     </row>
@@ -7200,52 +7364,52 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>大赛通知</t>
+          <t>中国高校数学建模课程中心</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+          <t>http://cumcm.icourses.cn/</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -7255,7 +7419,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：通知。</t>
+          <t>标题疑似导航/资讯/培训内容：课程中心。</t>
         </is>
       </c>
     </row>
@@ -7271,24 +7435,20 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>比赛时间: 2026.06.19</t>
-        </is>
-      </c>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>竞赛组织</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7298,32 +7458,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -7333,7 +7493,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：官方网站 移动版。</t>
+          <t>标题命中误抓取关键词：竞赛组织。</t>
         </is>
       </c>
     </row>
@@ -7349,59 +7509,55 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>比赛时间: 2026.06.19</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>挑战杯动态</t>
+          <t>苏州同元软控信息技术有限公司</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数学建模类</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
+          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.mcm.edu.cn/index.moma</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -7411,7 +7567,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：动态。</t>
+          <t>标题命中误抓取关键词：苏州同元软控信息技术有限公司。</t>
         </is>
       </c>
     </row>
@@ -7427,59 +7583,55 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>比赛时间: 6月1日</t>
-        </is>
-      </c>
+      <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>大数据和人工智能</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.datafountain.cn/competitions/1153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -7489,7 +7641,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
+          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
         </is>
       </c>
     </row>
@@ -7505,59 +7657,55 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>比赛时间: 6月1日</t>
-        </is>
-      </c>
+      <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（小挑）</t>
+          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>创新创业类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules2</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -7567,7 +7715,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
+          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
         </is>
       </c>
     </row>
@@ -7586,67 +7734,527 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>英语与财经表达类</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chinaneccs.cn/</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chinaneccs.cn/</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似编码异常或乱码。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>大赛通知</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>https://cy.ncss.cn/</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：通知。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 2026.06.19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>标题命中误抓取关键词：官方网站 移动版。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 2026.06.19</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯动态</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/tzb</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：动态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 6月1日</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>竞赛章程（大挑）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 6月1日</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>竞赛章程（小挑）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules2</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>疑似误抓取</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>竞赛简介</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>创新创业类</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/focus</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>标题疑似导航/资讯/培训内容：简介。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
+  <autoFilter ref="A1:P17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,12 +16,12 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3500,23 +3500,23 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>疑似误提取</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2009-20</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3551,19 +3551,19 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15843/</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -3571,14 +3571,14 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>日期数值超出有效范围。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
@@ -3667,12 +3667,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>6月1日</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
@@ -3750,67 +3750,145 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>竞赛章程（大挑）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>竞赛章程（小挑）</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>创新创业类</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P43"/>
+  <autoFilter ref="A1:P44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4437,7 +4515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6781,23 +6859,23 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>疑似误提取</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2009-20</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6832,19 +6910,19 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15843/</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -6852,14 +6930,14 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>日期数值超出有效范围。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -6934,8 +7012,86 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>结果公布/获奖公示</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯中国大学生创业计划竞赛</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>时间为周期性描述或需回源确认。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P32"/>
+  <autoFilter ref="A1:P33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,12 +16,12 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3500,23 +3500,23 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>疑似误提取</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15843/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3571,14 +3571,14 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>日期数值超出有效范围。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
@@ -3667,12 +3667,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>6月1日</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3707,27 +3707,27 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>竞赛章程（小挑）</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3809,86 +3809,8 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>正式比赛</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>6月1日</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>竞赛章程（小挑）</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/rules2</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P44"/>
+  <autoFilter ref="A1:P43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4515,7 +4437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6859,23 +6781,23 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>疑似误提取</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6910,12 +6832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15843/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6930,14 +6852,14 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>日期数值超出有效范围。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -7012,86 +6934,8 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>结果公布/获奖公示</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>时间为周期性描述或需回源确认。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P33"/>
+  <autoFilter ref="A1:P32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -548,12 +548,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026.06.19</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>中国国际大学生创新大赛</t>
+          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>挑战杯全国大学生课外学术科技作品竞赛</t>
+          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -734,37 +734,37 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://www.tiaozhanbei.net/article/15846/</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨第十五届“挑战杯”黑龙江省大学生创业计划竞赛终审决赛在东北林业大学举行</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15846/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -852,10 +852,14 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>标题命中误抓取关键词：官方网站 移动版。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -880,7 +884,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -895,7 +899,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -915,7 +919,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -930,14 +934,10 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>标题命中误抓取关键词：官方网站 移动版。</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -997,35 +997,39 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/tzb</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：动态。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1035,12 +1039,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026.06.19</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>挑战杯动态</t>
+          <t>中国国际大学生创新大赛</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1050,12 +1054,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>P3 低优先级</t>
+          <t>P2 可选参加</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1075,29 +1079,25 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：动态。</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -7848,7 +7848,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2025.zip</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2026.zip</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6946,7 +6946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7064,7 +7064,7 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026年全国大学生数学建模竞赛培训与应用研究研讨会第二次通知</t>
+          <t>SPSSPRO</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/3703fb7f6e16f999f45aac0593b1e1ff.html</t>
+          <t>https://www.spsspro.com/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：通知。</t>
+          <t>标题命中误抓取关键词：SPSSPRO。</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7138,7 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>SPSSPRO</t>
+          <t>《数学建模及其应用》</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://www.spsspro.com/?utm_source=cumcm</t>
+          <t>http://qxyy.cbpt.cnki.net</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：SPSSPRO。</t>
+          <t>标题命中误抓取关键词：《数学建模及其应用》。</t>
         </is>
       </c>
     </row>
@@ -7209,10 +7209,14 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>报名时间: 2026年9月10日</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>《数学建模及其应用》</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -7252,7 +7256,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>http://qxyy.cbpt.cnki.net</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7267,7 +7271,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：《数学建模及其应用》。</t>
+          <t>标题命中误抓取关键词：中国知网。</t>
         </is>
       </c>
     </row>
@@ -7283,14 +7287,10 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>报名时间: 2026年9月10日</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>中国高校数学建模课程中心</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>http://cumcm.icourses.cn/</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：中国知网。</t>
+          <t>标题疑似导航/资讯/培训内容：课程中心。</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>中国高校数学建模课程中心</t>
+          <t>竞赛组织</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.icourses.cn/</t>
+          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：课程中心。</t>
+          <t>标题命中误抓取关键词：竞赛组织。</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>竞赛组织</t>
+          <t>苏州同元软控信息技术有限公司</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/section/302f2c2355b1179ada9b99a06d7109f5.html</t>
+          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：竞赛组织。</t>
+          <t>标题命中误抓取关键词：苏州同元软控信息技术有限公司。</t>
         </is>
       </c>
     </row>
@@ -7512,12 +7512,12 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>苏州同元软控信息技术有限公司</t>
+          <t>大数据和人工智能</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>数学建模类</t>
+          <t>数据分析 / 统计建模类</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7542,22 +7542,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.tongyuan.cc/?utm_source=cumcm</t>
+          <t>https://www.datafountain.cn/competitions/1153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/index.moma</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：苏州同元软控信息技术有限公司。</t>
+          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>大数据和人工智能</t>
+          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions/1153</t>
+          <t>https://www.datafountain.cn/competitions</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7660,17 +7660,17 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>数据科学竞赛/大数据 Competitions - DataFountain</t>
+          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>数据分析 / 统计建模类</t>
+          <t>英语与财经表达类</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>P2 可选参加</t>
+          <t>P3 低优先级</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7690,22 +7690,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>https://www.datafountain.cn/competitions</t>
+          <t>https://www.chinaneccs.cn/</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>标题是平台栏目或泛化主题，不是明确比赛名称。</t>
+          <t>标题疑似编码异常或乱码。</t>
         </is>
       </c>
     </row>
@@ -7734,12 +7734,12 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>å ¨å½å¤§å­¦çè±è¯­ç«èµ-NECCS</t>
+          <t>大赛通知</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>英语与财经表达类</t>
+          <t>创新创业类</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -7769,17 +7769,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2026.zip</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>https://www.chinaneccs.cn/</t>
+          <t>https://cy.ncss.cn/</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>标题疑似编码异常或乱码。</t>
+          <t>标题疑似导航/资讯/培训内容：通知。</t>
         </is>
       </c>
     </row>
@@ -7805,10 +7805,14 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>比赛时间: 2026.06.19</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>大赛通知</t>
+          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -7823,7 +7827,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -7843,17 +7847,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://t3.chei.com.cn/ncss/cy/web/lib/dasaitongzhi-2026.zip</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>https://cy.ncss.cn/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -7863,7 +7867,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：通知。</t>
+          <t>标题命中误抓取关键词：官方网站 移动版。</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7890,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>挑战杯 全国大学生课外学术科技作品竞赛和创业计划大赛 官方网站 移动版</t>
+          <t>挑战杯动态</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -7901,7 +7905,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7926,14 +7930,14 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/tzb</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>是</t>
@@ -7941,7 +7945,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>标题命中误抓取关键词：官方网站 移动版。</t>
+          <t>标题疑似导航/资讯/培训内容：动态。</t>
         </is>
       </c>
     </row>
@@ -7959,12 +7963,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>比赛时间: 2026.06.19</t>
+          <t>比赛时间: 6月1日</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>挑战杯动态</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8004,7 +8008,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/tzb</t>
+          <t>https://www.tiaozhanbei.net/rules</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8019,7 +8023,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：动态。</t>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8046,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>竞赛章程（小挑）</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -8082,7 +8086,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8113,14 +8117,10 @@
           <t>疑似误抓取</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>比赛时间: 6月1日</t>
-        </is>
-      </c>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（小挑）</t>
+          <t>竞赛简介</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules2</t>
+          <t>https://www.tiaozhanbei.net/focus</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8175,86 +8175,12 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>疑似误抓取</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>竞赛简介</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/focus</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
           <t>标题疑似导航/资讯/培训内容：简介。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P17"/>
+  <autoFilter ref="A1:P16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,12 +16,12 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3500,23 +3500,23 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>疑似误提取</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2009-20</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3551,19 +3551,19 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15843/</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -3571,14 +3571,14 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>日期数值超出有效范围。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
@@ -3667,12 +3667,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>6月1日</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
@@ -3750,67 +3750,145 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>竞赛章程（大挑）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>正式比赛</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>6月1日</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>竞赛章程（小挑）</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>创新创业类</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>P3 低优先级</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P43"/>
+  <autoFilter ref="A1:P44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4437,7 +4515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6781,23 +6859,23 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>周期性/待核实</t>
+          <t>疑似误提取</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>2009-20</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6832,19 +6910,19 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/article/15843/</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -6852,14 +6930,14 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>日期数值超出有效范围。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -6934,8 +7012,86 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>结果公布/获奖公示</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>周期性/待核实</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>以年度通知为准</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>挑战杯中国大学生创业计划竞赛</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>创新创业类</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>P3 低优先级</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tiaozhanbei.net/</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>时间为周期性描述或需回源确认。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P32"/>
+  <autoFilter ref="A1:P33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/reports/schedule_report.xlsx
+++ b/reports/schedule_report.xlsx
@@ -16,12 +16,12 @@
     <sheet name="疑似误抓取" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'日程总览'!$A$1:$P$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'比赛时间优先'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'报名截止提醒'!$A$1:$P$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'结果公布提醒'!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'可进日历'!$A$1:$P$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核实'!$A$1:$P$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'疑似误抓取'!$A$1:$P$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3500,23 +3500,23 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>疑似误提取</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15843/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3571,14 +3571,14 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>日期数值超出有效范围。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>结果公布/获奖公示</t>
+          <t>正式比赛</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
@@ -3667,12 +3667,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>以年度通知为准</t>
+          <t>6月1日</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
+          <t>竞赛章程（大挑）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3707,27 +3707,27 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
+          <t>https://www.tiaozhanbei.net/rules</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
           <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>时间为周期性描述或需回源确认。</t>
+          <t>标题疑似导航/资讯/培训内容：章程。</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>竞赛章程（大挑）</t>
+          <t>竞赛章程（小挑）</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/rules</t>
+          <t>https://www.tiaozhanbei.net/rules2</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3809,86 +3809,8 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>正式比赛</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>6月1日</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>竞赛章程（小挑）</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/rules2</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>标题疑似导航/资讯/培训内容：章程。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P44"/>
+  <autoFilter ref="A1:P43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4515,7 +4437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6859,23 +6781,23 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>正式比赛</t>
+          <t>报名/报名截止</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>疑似误提取</t>
+          <t>周期性/待核实</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2009-20</t>
+          <t>以年度通知为准</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>挑战杯丨浙江省第十五届“挑战杯”大学生创业计划竞赛圆满落幕</t>
+          <t>挑战杯中国大学生创业计划竞赛</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6910,12 +6832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>https://www.tiaozhanbei.net/article/15843/</t>
+          <t>https://www.tiaozhanbei.net/</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6930,14 +6852,14 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>日期数值超出有效范围。</t>
+          <t>时间为周期性描述或需回源确认。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>报名/报名截止</t>
+          <t>结果公布/获奖公示</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -7012,86 +6934,8 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>结果公布/获奖公示</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>周期性/待核实</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>以年度通知为准</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>挑战杯中国大学生创业计划竞赛</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>创新创业类</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>P3 低优先级</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tiaozhanbei.net/</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>时间为周期性描述或需回源确认。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P33"/>
+  <autoFilter ref="A1:P32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
